--- a/product-definitions/spreadsheet/radon-concentration.xlsx
+++ b/product-definitions/spreadsheet/radon-concentration.xlsx
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -206,11 +206,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -235,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -262,17 +257,14 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -282,7 +274,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2087,26 +2079,26 @@
       <c r="F5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
     </row>
     <row r="6">
       <c r="A6" s="2"/>
@@ -2114,10 +2106,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2135,7 +2127,7 @@
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2144,7 +2136,7 @@
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -2153,7 +2145,7 @@
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2162,16 +2154,16 @@
       <c r="B11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2"/>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="13"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
         <v>27</v>
@@ -2191,14 +2183,14 @@
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="15"/>
+      <c r="C15" s="14"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
@@ -2245,15 +2237,15 @@
         <v>16</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="10"/>
-    </row>
-    <row r="21">
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -2262,57 +2254,57 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="12">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="14"/>
+      <c r="C26" s="13"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27">
+      <c r="K26" s="14"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
         <v>28</v>
@@ -2322,31 +2314,31 @@
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28">
+      <c r="K27" s="15"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29">
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30">
+      <c r="K28" s="15"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="C29" s="15"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
         <v>10</v>
@@ -2355,7 +2347,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
         <v>12</v>
@@ -2364,19 +2356,19 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
         <v>19</v>
@@ -2385,54 +2377,54 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="12">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="14"/>
+      <c r="C39" s="13"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2" t="s">
         <v>28</v>
@@ -2441,26 +2433,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42">
-      <c r="C42" s="16"/>
-    </row>
-    <row r="43">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="C42" s="15"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2" t="s">
         <v>10</v>
@@ -2469,7 +2461,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2" t="s">
         <v>12</v>
@@ -2478,18 +2470,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="6"/>
       <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2" t="s">
         <v>19</v>
@@ -2498,54 +2490,54 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C49" s="12">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C52" s="14"/>
+      <c r="C52" s="13"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
         <v>28</v>
@@ -2554,78 +2546,78 @@
         <v>29</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55">
-      <c r="C55" s="16"/>
-    </row>
-    <row r="56">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="C55" s="15"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B56" s="2"/>
-      <c r="C56" s="15"/>
-    </row>
-    <row r="57">
+      <c r="C56" s="14"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="15">
         <v>1.0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="16"/>
-    </row>
-    <row r="61">
+      <c r="C60" s="15"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="8" t="s">
         <v>46</v>
@@ -2635,604 +2627,604 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="C64" s="16"/>
+      <c r="C64" s="15"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="C65" s="16"/>
+      <c r="C65" s="15"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="C66" s="16"/>
+      <c r="C66" s="15"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="C67" s="16"/>
+      <c r="C67" s="15"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="C68" s="16"/>
+      <c r="C68" s="15"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="C69" s="16"/>
+      <c r="C69" s="15"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="C70" s="16"/>
+      <c r="C70" s="15"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="C71" s="16"/>
+      <c r="C71" s="15"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="C72" s="16"/>
+      <c r="C72" s="15"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="C73" s="16"/>
+      <c r="C73" s="15"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="C74" s="16"/>
+      <c r="C74" s="15"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="C75" s="16"/>
+      <c r="C75" s="15"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="C76" s="16"/>
+      <c r="C76" s="15"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="C77" s="16"/>
+      <c r="C77" s="15"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="C78" s="16"/>
+      <c r="C78" s="15"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="C79" s="16"/>
+      <c r="C79" s="15"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="C80" s="16"/>
+      <c r="C80" s="15"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="C81" s="16"/>
+      <c r="C81" s="15"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="C82" s="16"/>
+      <c r="C82" s="15"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="C83" s="16"/>
+      <c r="C83" s="15"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="C84" s="16"/>
+      <c r="C84" s="15"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="C85" s="16"/>
+      <c r="C85" s="15"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="C86" s="16"/>
+      <c r="C86" s="15"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="C87" s="16"/>
+      <c r="C87" s="15"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="C88" s="16"/>
+      <c r="C88" s="15"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="C89" s="16"/>
+      <c r="C89" s="15"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="C90" s="16"/>
+      <c r="C90" s="15"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="C91" s="16"/>
+      <c r="C91" s="15"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="C92" s="16"/>
+      <c r="C92" s="15"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="C93" s="16"/>
+      <c r="C93" s="15"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="C94" s="16"/>
+      <c r="C94" s="15"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="C95" s="16"/>
+      <c r="C95" s="15"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="C96" s="16"/>
+      <c r="C96" s="15"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="C97" s="16"/>
+      <c r="C97" s="15"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="C98" s="16"/>
+      <c r="C98" s="15"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="C99" s="16"/>
+      <c r="C99" s="15"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="C100" s="16"/>
+      <c r="C100" s="15"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="C101" s="16"/>
+      <c r="C101" s="15"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="C102" s="16"/>
+      <c r="C102" s="15"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="C103" s="16"/>
+      <c r="C103" s="15"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="C104" s="16"/>
+      <c r="C104" s="15"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="C105" s="16"/>
+      <c r="C105" s="15"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="C106" s="16"/>
+      <c r="C106" s="15"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="C107" s="16"/>
+      <c r="C107" s="15"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="C108" s="16"/>
+      <c r="C108" s="15"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="C109" s="16"/>
+      <c r="C109" s="15"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="C110" s="16"/>
+      <c r="C110" s="15"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="C111" s="16"/>
+      <c r="C111" s="15"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="C112" s="16"/>
+      <c r="C112" s="15"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="C113" s="16"/>
+      <c r="C113" s="15"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="C114" s="16"/>
+      <c r="C114" s="15"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="C115" s="16"/>
+      <c r="C115" s="15"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="C116" s="16"/>
+      <c r="C116" s="15"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="C117" s="16"/>
+      <c r="C117" s="15"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="C118" s="16"/>
+      <c r="C118" s="15"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="C119" s="16"/>
+      <c r="C119" s="15"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="C120" s="16"/>
+      <c r="C120" s="15"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="C121" s="16"/>
+      <c r="C121" s="15"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="C122" s="16"/>
+      <c r="C122" s="15"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="C123" s="16"/>
+      <c r="C123" s="15"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="C124" s="16"/>
+      <c r="C124" s="15"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="C125" s="16"/>
+      <c r="C125" s="15"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="C126" s="16"/>
+      <c r="C126" s="15"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="C127" s="16"/>
+      <c r="C127" s="15"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="C128" s="16"/>
+      <c r="C128" s="15"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="C129" s="16"/>
+      <c r="C129" s="15"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="C130" s="16"/>
+      <c r="C130" s="15"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="C131" s="16"/>
+      <c r="C131" s="15"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="C132" s="16"/>
+      <c r="C132" s="15"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="C133" s="16"/>
+      <c r="C133" s="15"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="C134" s="16"/>
+      <c r="C134" s="15"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="C135" s="16"/>
+      <c r="C135" s="15"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="C136" s="16"/>
+      <c r="C136" s="15"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="C137" s="16"/>
+      <c r="C137" s="15"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="C138" s="16"/>
+      <c r="C138" s="15"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="C139" s="16"/>
+      <c r="C139" s="15"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="C140" s="16"/>
+      <c r="C140" s="15"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="C141" s="16"/>
+      <c r="C141" s="15"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="C142" s="16"/>
+      <c r="C142" s="15"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="C143" s="16"/>
+      <c r="C143" s="15"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="C144" s="16"/>
+      <c r="C144" s="15"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="C145" s="16"/>
+      <c r="C145" s="15"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="C146" s="16"/>
+      <c r="C146" s="15"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="C147" s="16"/>
+      <c r="C147" s="15"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="C148" s="16"/>
+      <c r="C148" s="15"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="C149" s="16"/>
+      <c r="C149" s="15"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="C150" s="16"/>
+      <c r="C150" s="15"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="C151" s="16"/>
+      <c r="C151" s="15"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="C152" s="16"/>
+      <c r="C152" s="15"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="C153" s="16"/>
+      <c r="C153" s="15"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="C154" s="16"/>
+      <c r="C154" s="15"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="C155" s="16"/>
+      <c r="C155" s="15"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="C156" s="16"/>
+      <c r="C156" s="15"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="C157" s="16"/>
+      <c r="C157" s="15"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="C158" s="16"/>
+      <c r="C158" s="15"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="C159" s="16"/>
+      <c r="C159" s="15"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="C160" s="16"/>
+      <c r="C160" s="15"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="C161" s="16"/>
+      <c r="C161" s="15"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="C162" s="16"/>
+      <c r="C162" s="15"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="C163" s="16"/>
+      <c r="C163" s="15"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="C164" s="16"/>
+      <c r="C164" s="15"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="C165" s="16"/>
+      <c r="C165" s="15"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="C166" s="16"/>
+      <c r="C166" s="15"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="C167" s="16"/>
+      <c r="C167" s="15"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="C168" s="16"/>
+      <c r="C168" s="15"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="C169" s="16"/>
+      <c r="C169" s="15"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="C170" s="16"/>
+      <c r="C170" s="15"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="C171" s="16"/>
+      <c r="C171" s="15"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="C172" s="16"/>
+      <c r="C172" s="15"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="C173" s="16"/>
+      <c r="C173" s="15"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="C174" s="16"/>
+      <c r="C174" s="15"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="16"/>
+      <c r="C175" s="15"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="C176" s="16"/>
+      <c r="C176" s="15"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="C177" s="16"/>
+      <c r="C177" s="15"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="C178" s="16"/>
+      <c r="C178" s="15"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="16"/>
+      <c r="C179" s="15"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="C180" s="16"/>
+      <c r="C180" s="15"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="C181" s="16"/>
+      <c r="C181" s="15"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="C182" s="16"/>
+      <c r="C182" s="15"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="C183" s="16"/>
+      <c r="C183" s="15"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="C184" s="16"/>
+      <c r="C184" s="15"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="C185" s="16"/>
+      <c r="C185" s="15"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="C186" s="16"/>
+      <c r="C186" s="15"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="C187" s="16"/>
+      <c r="C187" s="15"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="C188" s="16"/>
+      <c r="C188" s="15"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="C189" s="16"/>
+      <c r="C189" s="15"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="C190" s="16"/>
+      <c r="C190" s="15"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="C191" s="16"/>
+      <c r="C191" s="15"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="C192" s="16"/>
+      <c r="C192" s="15"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="C193" s="16"/>
+      <c r="C193" s="15"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="C194" s="16"/>
+      <c r="C194" s="15"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="C195" s="16"/>
+      <c r="C195" s="15"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="C196" s="16"/>
+      <c r="C196" s="15"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="C197" s="16"/>
+      <c r="C197" s="15"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="C198" s="16"/>
+      <c r="C198" s="15"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="C199" s="16"/>
+      <c r="C199" s="15"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="C200" s="16"/>
+      <c r="C200" s="15"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="C201" s="16"/>
+      <c r="C201" s="15"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="C202" s="16"/>
+      <c r="C202" s="15"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="16"/>
+      <c r="C203" s="15"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="C204" s="16"/>
+      <c r="C204" s="15"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="C205" s="16"/>
+      <c r="C205" s="15"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="C206" s="16"/>
+      <c r="C206" s="15"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="C207" s="16"/>
+      <c r="C207" s="15"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="C208" s="16"/>
+      <c r="C208" s="15"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="C209" s="16"/>
+      <c r="C209" s="15"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="C210" s="16"/>
+      <c r="C210" s="15"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="C211" s="16"/>
+      <c r="C211" s="15"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="C212" s="16"/>
+      <c r="C212" s="15"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="C213" s="16"/>
+      <c r="C213" s="15"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="C214" s="16"/>
+      <c r="C214" s="15"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="C215" s="16"/>
+      <c r="C215" s="15"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="C216" s="16"/>
+      <c r="C216" s="15"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="C217" s="16"/>
+      <c r="C217" s="15"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="16"/>
+      <c r="C218" s="15"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="C219" s="16"/>
+      <c r="C219" s="15"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="C220" s="16"/>
+      <c r="C220" s="15"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="C221" s="16"/>
+      <c r="C221" s="15"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="C222" s="16"/>
+      <c r="C222" s="15"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="C223" s="16"/>
+      <c r="C223" s="15"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="C224" s="16"/>
+      <c r="C224" s="15"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="C225" s="16"/>
+      <c r="C225" s="15"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="C226" s="16"/>
+      <c r="C226" s="15"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="C227" s="16"/>
+      <c r="C227" s="15"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="C228" s="16"/>
+      <c r="C228" s="15"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="C229" s="16"/>
+      <c r="C229" s="15"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="C230" s="16"/>
+      <c r="C230" s="15"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="C231" s="16"/>
+      <c r="C231" s="15"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="C232" s="16"/>
+      <c r="C232" s="15"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="C233" s="16"/>
+      <c r="C233" s="15"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="C234" s="16"/>
+      <c r="C234" s="15"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="C235" s="16"/>
+      <c r="C235" s="15"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="C236" s="16"/>
+      <c r="C236" s="15"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="C237" s="16"/>
+      <c r="C237" s="15"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="C238" s="16"/>
+      <c r="C238" s="15"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="C239" s="16"/>
+      <c r="C239" s="15"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="C240" s="16"/>
+      <c r="C240" s="15"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="C241" s="16"/>
+      <c r="C241" s="15"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="C242" s="16"/>
+      <c r="C242" s="15"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="C243" s="16"/>
+      <c r="C243" s="15"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="C244" s="16"/>
+      <c r="C244" s="15"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="C245" s="16"/>
+      <c r="C245" s="15"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="C246" s="16"/>
+      <c r="C246" s="15"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="C247" s="16"/>
+      <c r="C247" s="15"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="C248" s="16"/>
+      <c r="C248" s="15"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="C249" s="16"/>
+      <c r="C249" s="15"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="C250" s="16"/>
+      <c r="C250" s="15"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="C251" s="16"/>
+      <c r="C251" s="15"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="C252" s="16"/>
+      <c r="C252" s="15"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="C253" s="16"/>
+      <c r="C253" s="15"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="C254" s="16"/>
+      <c r="C254" s="15"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="C255" s="16"/>
+      <c r="C255" s="15"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="C256" s="16"/>
+      <c r="C256" s="15"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="C257" s="16"/>
+      <c r="C257" s="15"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="C258" s="16"/>
+      <c r="C258" s="15"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="C259" s="16"/>
+      <c r="C259" s="15"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="C260" s="16"/>
+      <c r="C260" s="15"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="C261" s="16"/>
+      <c r="C261" s="15"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="C262" s="16"/>
+      <c r="C262" s="15"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="C263" s="16"/>
+      <c r="C263" s="15"/>
     </row>
     <row r="264" ht="15.75" customHeight="1"/>
     <row r="265" ht="15.75" customHeight="1"/>
